--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -35966,23 +35966,19 @@
       </c>
       <c r="F508" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H508" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I508" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="H508" s="5" t="n">
+        <v>17975000</v>
+      </c>
+      <c r="I508" s="5" t="n">
+        <v>27153</v>
       </c>
       <c r="J508" s="3" t="inlineStr">
         <is>
@@ -35991,12 +35987,12 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M508" s="3" t="inlineStr">
@@ -36006,7 +36002,7 @@
       </c>
       <c r="N508" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38797,7 +38793,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38807,7 +38803,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -40929,12 +40925,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="22" t="inlineStr">
+      <c r="E31" s="23" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
-招标单位
--
-(在售)</t>
+$1798万
+$27,153/呎
+(26年-09月-07日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -27403,7 +27403,7 @@
       </c>
       <c r="G384" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H384" s="5" t="n">
@@ -28025,7 +28025,7 @@
       </c>
       <c r="G393" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="H393" s="5" t="n">
@@ -39808,7 +39808,7 @@
           <t>B | 667呎 (3房)
 $2415万
 $36,201/呎
-(26年-08月-12日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
@@ -39887,7 +39887,7 @@
           <t>B | 667呎 (3房)
 $2403万
 $36,021/呎
-(26年-08月-12日)</t>
+(26年-09月-11日)</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -31003,7 +31003,7 @@
       </c>
       <c r="G436" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="H436" s="5" t="n">
@@ -40298,7 +40298,7 @@
           <t>D | 662呎 (3房)
 $1919万
 $28,986/呎
-(26年-08月-31日)</t>
+(26年-09月-23日)</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -270,10 +270,10 @@
     <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="F104" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G104" s="3" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H104" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I104" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J104" s="3" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M104" s="3" t="inlineStr">
@@ -7878,7 +7878,7 @@
       </c>
       <c r="N104" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -8538,7 +8538,7 @@
       </c>
       <c r="F114" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G114" s="3" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="H114" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I114" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J114" s="3" t="inlineStr">
@@ -8563,12 +8563,12 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M114" s="3" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="N114" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -11338,7 +11338,7 @@
       </c>
       <c r="F154" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G154" s="3" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="H154" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I154" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J154" s="3" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M154" s="3" t="inlineStr">
@@ -11378,7 +11378,7 @@
       </c>
       <c r="N154" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12738,7 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
@@ -12748,12 +12748,12 @@
       </c>
       <c r="H174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J174" s="3" t="inlineStr">
@@ -12763,12 +12763,12 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="N174" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13438,7 +13438,7 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
@@ -13448,12 +13448,12 @@
       </c>
       <c r="H184" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I184" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J184" s="3" t="inlineStr">
@@ -13463,12 +13463,12 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="N184" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15538,7 +15538,7 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
@@ -15548,12 +15548,12 @@
       </c>
       <c r="H214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J214" s="3" t="inlineStr">
@@ -15563,12 +15563,12 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="N214" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16238,7 +16238,7 @@
       </c>
       <c r="F224" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G224" s="3" t="inlineStr">
@@ -16248,12 +16248,12 @@
       </c>
       <c r="H224" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I224" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J224" s="3" t="inlineStr">
@@ -16263,12 +16263,12 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M224" s="3" t="inlineStr">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="N224" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G234" s="3" t="inlineStr">
@@ -16948,12 +16948,12 @@
       </c>
       <c r="H234" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I234" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J234" s="3" t="inlineStr">
@@ -16963,12 +16963,12 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M234" s="3" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="N234" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -36286,27 +36286,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
+      <c r="D3" s="16" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D3" s="16" t="inlineStr">
+      <c r="E3" s="17" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>270</t>
+          <t>262</t>
         </is>
       </c>
     </row>
@@ -37307,12 +37307,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J15" s="20" t="inlineStr">
+      <c r="J15" s="21" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="K15" s="20" t="inlineStr">
@@ -37394,12 +37394,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J16" s="20" t="inlineStr">
+      <c r="J16" s="21" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="K16" s="20" t="inlineStr">
@@ -37742,12 +37742,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J20" s="20" t="inlineStr">
+      <c r="J20" s="21" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="K20" s="20" t="inlineStr">
@@ -37916,12 +37916,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J22" s="20" t="inlineStr">
+      <c r="J22" s="21" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -38003,12 +38003,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J23" s="20" t="inlineStr">
+      <c r="J23" s="21" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="K23" s="20" t="inlineStr">
@@ -38264,12 +38264,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J26" s="20" t="inlineStr">
+      <c r="J26" s="21" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">
@@ -38351,12 +38351,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J27" s="20" t="inlineStr">
+      <c r="J27" s="21" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="K27" s="20" t="inlineStr">
@@ -38438,12 +38438,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J28" s="20" t="inlineStr">
+      <c r="J28" s="21" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="K28" s="20" t="inlineStr">
@@ -38883,7 +38883,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="21" t="inlineStr"/>
+      <c r="C5" s="22" t="inlineStr"/>
       <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 752呎 (3房)
@@ -38892,9 +38892,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr"/>
-      <c r="F5" s="21" t="inlineStr"/>
-      <c r="G5" s="21" t="inlineStr"/>
+      <c r="E5" s="22" t="inlineStr"/>
+      <c r="F5" s="22" t="inlineStr"/>
+      <c r="G5" s="22" t="inlineStr"/>
       <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 448呎 (2房)
@@ -38934,7 +38934,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 招标单位
@@ -39013,7 +39013,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 招标单位
@@ -39250,7 +39250,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="21" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 招标单位
@@ -39329,7 +39329,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 招标单位
@@ -39400,7 +39400,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 招标单位
@@ -39408,7 +39408,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="21" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 招标单位
@@ -39503,7 +39503,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="21" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 招标单位
@@ -39582,7 +39582,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="21" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 招标单位
@@ -40056,7 +40056,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="21" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 招标单位
@@ -40214,7 +40214,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 招标单位
@@ -40609,7 +40609,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E27" s="22" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 招标单位
@@ -40688,7 +40688,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E28" s="22" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 招标单位
@@ -40846,7 +40846,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E30" s="22" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 招标单位

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -23020,23 +23020,19 @@
       </c>
       <c r="F321" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H321" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I321" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="H321" s="5" t="n">
+        <v>25828000</v>
+      </c>
+      <c r="I321" s="5" t="n">
+        <v>38723</v>
       </c>
       <c r="J321" s="3" t="inlineStr">
         <is>
@@ -23045,12 +23041,12 @@
       </c>
       <c r="K321" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L321" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M321" s="3" t="inlineStr">
@@ -23060,7 +23056,7 @@
       </c>
       <c r="N321" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -38793,7 +38789,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -38803,7 +38799,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -39250,12 +39246,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="21" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
-招标单位
--
-(在售)</t>
+$2583万
+$38,723/呎
+(26年-10月-02日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -273,10 +273,10 @@
     <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -12738,23 +12738,19 @@
       </c>
       <c r="F174" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H174" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I174" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="H174" s="5" t="n">
+        <v>17766000</v>
+      </c>
+      <c r="I174" s="5" t="n">
+        <v>32011</v>
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
@@ -12763,12 +12759,12 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M174" s="3" t="inlineStr">
@@ -12778,7 +12774,7 @@
       </c>
       <c r="N174" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36282,7 +36278,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -36292,7 +36288,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -37912,12 +37908,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J22" s="21" t="inlineStr">
+      <c r="J22" s="22" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
-招标单位
--
-(在售)</t>
+$1777万
+$32,011/呎
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
@@ -38879,7 +38875,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr"/>
+      <c r="C5" s="23" t="inlineStr"/>
       <c r="D5" s="20" t="inlineStr">
         <is>
           <t>C | 752呎 (3房)
@@ -38888,9 +38884,9 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E5" s="22" t="inlineStr"/>
-      <c r="F5" s="22" t="inlineStr"/>
-      <c r="G5" s="22" t="inlineStr"/>
+      <c r="E5" s="23" t="inlineStr"/>
+      <c r="F5" s="23" t="inlineStr"/>
+      <c r="G5" s="23" t="inlineStr"/>
       <c r="H5" s="20" t="inlineStr">
         <is>
           <t>G | 448呎 (2房)
@@ -39088,7 +39084,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2576万
@@ -39167,7 +39163,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2551万
@@ -39246,7 +39242,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2583万
@@ -39475,7 +39471,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $3211万
@@ -39483,7 +39479,7 @@
 (26年-05月-18日)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2463万
@@ -39554,7 +39550,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2663万
@@ -39562,7 +39558,7 @@
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2236万
@@ -39633,7 +39629,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2575万
@@ -39641,7 +39637,7 @@
 (26年-04月-21日)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2225万
@@ -39712,7 +39708,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $3069万
@@ -39720,7 +39716,7 @@
 (26年-05月-19日)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2342万
@@ -39791,7 +39787,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $3094万
@@ -39799,7 +39795,7 @@
 (26年-05月-21日)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2415万
@@ -39870,7 +39866,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $3080万
@@ -39878,7 +39874,7 @@
 (26年-06月-01日)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2403万
@@ -39949,7 +39945,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2524万
@@ -39957,7 +39953,7 @@
 (26年-04月-30日)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2181万
@@ -40028,7 +40024,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2512万
@@ -40036,7 +40032,7 @@
 (26年-04月-23日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2295万
@@ -40186,7 +40182,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2985万
@@ -40194,7 +40190,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2220万
@@ -40265,7 +40261,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2462万
@@ -40273,7 +40269,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2127万
@@ -40289,7 +40285,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 $1919万
@@ -40344,7 +40340,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2450万
@@ -40352,7 +40348,7 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2116万
@@ -40368,7 +40364,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 $1909万
@@ -40423,7 +40419,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2437万
@@ -40431,7 +40427,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2106万
@@ -40502,7 +40498,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2425万
@@ -40510,7 +40506,7 @@
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2135万
@@ -40581,7 +40577,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B27" s="23" t="inlineStr">
+      <c r="B27" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2413万
@@ -40589,7 +40585,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="C27" s="23" t="inlineStr">
+      <c r="C27" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2245万
@@ -40660,7 +40656,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B28" s="23" t="inlineStr">
+      <c r="B28" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2401万
@@ -40668,7 +40664,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="C28" s="23" t="inlineStr">
+      <c r="C28" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2212万
@@ -40739,7 +40735,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2388万
@@ -40747,7 +40743,7 @@
 (26年-04月-22日)</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2195万
@@ -40818,7 +40814,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2364万
@@ -40826,7 +40822,7 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $2151万
@@ -40897,7 +40893,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B31" s="23" t="inlineStr">
+      <c r="B31" s="22" t="inlineStr">
         <is>
           <t>A | 744呎 (3房)
 $2306万
@@ -40905,7 +40901,7 @@
 (26年-05月-08日)</t>
         </is>
       </c>
-      <c r="C31" s="23" t="inlineStr">
+      <c r="C31" s="22" t="inlineStr">
         <is>
           <t>B | 667呎 (3房)
 $1951万
@@ -40921,7 +40917,7 @@
 (待售)</t>
         </is>
       </c>
-      <c r="E31" s="23" t="inlineStr">
+      <c r="E31" s="22" t="inlineStr">
         <is>
           <t>D | 662呎 (3房)
 $1798万

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -35963,7 +35963,7 @@
       </c>
       <c r="G508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="H508" s="5" t="n">
@@ -40922,7 +40922,7 @@
           <t>D | 662呎 (3房)
 $1798万
 $27,153/呎
-(26年-09月-07日)</t>
+(26年-10月-09日)</t>
         </is>
       </c>
       <c r="F31" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -10638,7 +10638,7 @@
       </c>
       <c r="F144" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G144" s="3" t="inlineStr">
@@ -10648,12 +10648,12 @@
       </c>
       <c r="H144" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I144" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J144" s="3" t="inlineStr">
@@ -10663,12 +10663,12 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M144" s="3" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="N144" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -13434,23 +13434,19 @@
       </c>
       <c r="F184" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H184" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I184" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="H184" s="5" t="n">
+        <v>17677000</v>
+      </c>
+      <c r="I184" s="5" t="n">
+        <v>31850</v>
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
@@ -13459,12 +13455,12 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M184" s="3" t="inlineStr">
@@ -13474,7 +13470,7 @@
       </c>
       <c r="N184" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -14134,7 +14130,7 @@
       </c>
       <c r="F194" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G194" s="3" t="inlineStr">
@@ -14144,12 +14140,12 @@
       </c>
       <c r="H194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J194" s="3" t="inlineStr">
@@ -14159,12 +14155,12 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M194" s="3" t="inlineStr">
@@ -14174,7 +14170,7 @@
       </c>
       <c r="N194" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -15534,23 +15530,19 @@
       </c>
       <c r="F214" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H214" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I214" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="H214" s="5" t="n">
+        <v>17413000</v>
+      </c>
+      <c r="I214" s="5" t="n">
+        <v>31375</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
@@ -15559,12 +15551,12 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M214" s="3" t="inlineStr">
@@ -15574,7 +15566,7 @@
       </c>
       <c r="N214" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -36288,7 +36280,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -36298,7 +36290,7 @@
       </c>
       <c r="F3" s="18" t="inlineStr">
         <is>
-          <t>262</t>
+          <t>260</t>
         </is>
       </c>
     </row>
@@ -37647,12 +37639,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J19" s="20" t="inlineStr">
+      <c r="J19" s="21" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
--
--
-(待售)</t>
+招标单位
+-
+(在售)</t>
         </is>
       </c>
       <c r="K19" s="20" t="inlineStr">
@@ -37995,7 +37987,94 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J23" s="21" t="inlineStr">
+      <c r="J23" s="22" t="inlineStr">
+        <is>
+          <t>J | 555呎 (2房)
+$1768万
+$31,850/呎
+(26年-10月-13日)</t>
+        </is>
+      </c>
+      <c r="K23" s="20" t="inlineStr">
+        <is>
+          <t>K | 570呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 487呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 311呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="inlineStr">
+        <is>
+          <t>D | 305呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F24" s="20" t="inlineStr">
+        <is>
+          <t>E | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G24" s="20" t="inlineStr">
+        <is>
+          <t>F | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
+        <is>
+          <t>G | 308呎 (1房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="I24" s="20" t="inlineStr">
+        <is>
+          <t>H | 465呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="J24" s="21" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
 招标单位
@@ -38003,93 +38082,6 @@
 (在售)</t>
         </is>
       </c>
-      <c r="K23" s="20" t="inlineStr">
-        <is>
-          <t>K | 570呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="58" customHeight="1">
-      <c r="A24" s="19" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B24" s="20" t="inlineStr">
-        <is>
-          <t>A | 487呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>B | 490呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>C | 311呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>D | 305呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>E | 308呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>F | 308呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>G | 308呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="I24" s="20" t="inlineStr">
-        <is>
-          <t>H | 465呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="J24" s="20" t="inlineStr">
-        <is>
-          <t>J | 555呎 (2房)
--
--
-(待售)</t>
-        </is>
-      </c>
       <c r="K24" s="20" t="inlineStr">
         <is>
           <t>K | 570呎 (2房)
@@ -38256,12 +38248,12 @@
 (待售)</t>
         </is>
       </c>
-      <c r="J26" s="21" t="inlineStr">
+      <c r="J26" s="22" t="inlineStr">
         <is>
           <t>J | 555呎 (2房)
-招标单位
--
-(在售)</t>
+$1741万
+$31,375/呎
+(26年-10月-14日)</t>
         </is>
       </c>
       <c r="K26" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -23013,7 +23013,7 @@
       </c>
       <c r="G321" s="3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="H321" s="5" t="n">
@@ -39239,7 +39239,7 @@
           <t>B | 667呎 (3房)
 $2583万
 $38,723/呎
-(26年-10月-02日)</t>
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="D10" s="20" t="inlineStr">

--- a/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
+++ b/九龙-启德-维港．湾畔第2B期/维港．湾畔第2B期_销控明细表.xlsx
@@ -12743,7 +12743,7 @@
       </c>
       <c r="G174" s="3" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-28</t>
         </is>
       </c>
       <c r="H174" s="5" t="n">
@@ -37905,7 +37905,7 @@
           <t>J | 555呎 (2房)
 $1777万
 $32,011/呎
-(26年-10月-05日)</t>
+(26年-10月-28日)</t>
         </is>
       </c>
       <c r="K22" s="20" t="inlineStr">
